--- a/20250421_Glidepath/01_source/Glidepath/Product List.xlsx
+++ b/20250421_Glidepath/01_source/Glidepath/Product List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eliza\Downloads\Glidepath\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/i0515899/Documents/Git/AI_Power_Studio/20250421_Glidepath/01_source/Glidepath/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9038A33B-C082-46E4-A612-B3DB33C53BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8E052E-59A4-4444-9F13-E12AF61DB002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{09C06BC0-1D42-4E82-BE7B-29001A0B4E97}"/>
+    <workbookView xWindow="-23200" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{09C06BC0-1D42-4E82-BE7B-29001A0B4E97}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -2884,9 +2884,9 @@
     <definedName name="estragofumo1" hidden="1">{#N/A,#N/A,TRUE,"Start";#N/A,#N/A,TRUE,"DadosGerais";#N/A,#N/A,TRUE,"Custo Conversão"}</definedName>
     <definedName name="estragofumo100" hidden="1">{#N/A,#N/A,FALSE,"CAPA";#N/A,#N/A,FALSE,"VOLUME DE PRODUÇÃO";#N/A,#N/A,FALSE,"MÃO DE OBRA TOTAL";#N/A,#N/A,FALSE,"HEAD-COUNT MENSALISTAS";#N/A,#N/A,FALSE,"HEAD-COUNT EXECUTIVOS";#N/A,#N/A,FALSE,"HEAD-COUNT EXEC. - ABERTURA";#N/A,#N/A,FALSE,"DESPESAS POR C. C.";#N/A,#N/A,FALSE,"PRODUTIVIDADE - PMM";#N/A,#N/A,FALSE,"PRODUTIVIDADE - PMT";#N/A,#N/A,FALSE,"PRODUTIVIDADE ACUMULADA - PMM";#N/A,#N/A,FALSE,"PRODUTIVIDADE ACUMULADA - PMT";#N/A,#N/A,FALSE,"ANÁLISE DE EFICIÊNCIA";#N/A,#N/A,FALSE,"ESTRAGOS"}</definedName>
     <definedName name="esttttt" hidden="1">{#N/A,#N/A,FALSE,"CAPA";#N/A,#N/A,FALSE,"VOLUME DE PRODUÇÃO";#N/A,#N/A,FALSE,"MÃO DE OBRA TOTAL";#N/A,#N/A,FALSE,"HEAD-COUNT MENSALISTAS";#N/A,#N/A,FALSE,"HEAD-COUNT EXECUTIVOS";#N/A,#N/A,FALSE,"HEAD-COUNT EXEC. - ABERTURA";#N/A,#N/A,FALSE,"DESPESAS POR C. C.";#N/A,#N/A,FALSE,"PRODUTIVIDADE - PMM";#N/A,#N/A,FALSE,"PRODUTIVIDADE - PMT";#N/A,#N/A,FALSE,"PRODUTIVIDADE ACUMULADA - PMM";#N/A,#N/A,FALSE,"PRODUTIVIDADE ACUMULADA - PMT";#N/A,#N/A,FALSE,"ANÁLISE DE EFICIÊNCIA";#N/A,#N/A,FALSE,"ESTRAGOS"}</definedName>
+    <definedName name="EV__LASTREFTIME__" hidden="1">39105.4848842593</definedName>
     <definedName name="ev.Calculation" hidden="1">-4135</definedName>
     <definedName name="ev.Initialized" hidden="1">FALSE</definedName>
-    <definedName name="EV__LASTREFTIME__" hidden="1">39105.4848842593</definedName>
     <definedName name="ewqwefr" hidden="1">{#N/A,#N/A,TRUE,"ReportFrontPage";#N/A,#N/A,TRUE,"CostSummary"}</definedName>
     <definedName name="ewweeewwww" hidden="1">#REF!</definedName>
     <definedName name="ewwewwweeww" hidden="1">{#N/A,#N/A,FALSE,"Cover";#N/A,#N/A,FALSE,"Index";#N/A,#N/A,FALSE,"Political and Economic";#N/A,#N/A,FALSE,"General Mngr's Overview B 1.1";#N/A,#N/A,FALSE,"Sales B 2.1";#N/A,#N/A,FALSE,"NSR B 2.2";#N/A,#N/A,FALSE,"Operations - Leaf B 3.1";#N/A,#N/A,FALSE,"Operations - Mnf B 3.2";#N/A,#N/A,FALSE,"CORA B 4.1";#N/A,#N/A,FALSE,"HR B 5.1";#N/A,#N/A,FALSE,"Finance Overview C 1.1";#N/A,#N/A,FALSE,"Profit and Loss C 2.1";#N/A,#N/A,FALSE,"Production - Leaf C 3.1";#N/A,#N/A,FALSE,"Production - Mnfg C 3.2";#N/A,#N/A,FALSE,"Balance Sheet C 4.1";#N/A,#N/A,FALSE,"Cash Flow C 5.1";#N/A,#N/A,FALSE,"Aged Debtors C 6.1"}</definedName>
@@ -3200,6 +3200,7 @@
     <definedName name="qqqqqqqqqqqqqqqqqqqq" hidden="1">#REF!</definedName>
     <definedName name="qqqqqqqqqqqqqqqqqqqqqq" hidden="1">#REF!</definedName>
     <definedName name="RCArea" hidden="1">#REF!</definedName>
+    <definedName name="_xlnm.Recorder" hidden="1">#REF!</definedName>
     <definedName name="red" hidden="1">{#N/A,#N/A,FALSE,"Aging Summary";#N/A,#N/A,FALSE,"Ratio Analysis";#N/A,#N/A,FALSE,"Test 120 Day Accts";#N/A,#N/A,FALSE,"Tickmarks"}</definedName>
     <definedName name="rim" hidden="1">#REF!</definedName>
     <definedName name="RiskAfterRecalcMacro" hidden="1">"DataOutputEOI"</definedName>
@@ -3453,17 +3454,16 @@
     <definedName name="Z_E2699901_D040_11D0_A510_006097B38048_.wvu.FilterData" hidden="1">#REF!</definedName>
     <definedName name="zxdtgz" hidden="1">#REF!</definedName>
     <definedName name="ZZZZZZZZZZZZZZZZZZZZZZ" hidden="1">{#N/A,#N/A,FALSE,"CAPA";#N/A,#N/A,FALSE,"VOLUME DE PRODUÇÃO";#N/A,#N/A,FALSE,"MÃO DE OBRA TOTAL";#N/A,#N/A,FALSE,"HEAD-COUNT MENSALISTAS";#N/A,#N/A,FALSE,"HEAD-COUNT EXECUTIVOS";#N/A,#N/A,FALSE,"HEAD-COUNT EXEC. - ABERTURA";#N/A,#N/A,FALSE,"DESPESAS POR C. C.";#N/A,#N/A,FALSE,"PRODUTIVIDADE - PMM";#N/A,#N/A,FALSE,"PRODUTIVIDADE - PMT";#N/A,#N/A,FALSE,"PRODUTIVIDADE ACUMULADA - PMM";#N/A,#N/A,FALSE,"PRODUTIVIDADE ACUMULADA - PMT";#N/A,#N/A,FALSE,"ANÁLISE DE EFICIÊNCIA";#N/A,#N/A,FALSE,"ESTRAGOS"}</definedName>
+    <definedName name="产成品入库单22">#REF!</definedName>
     <definedName name="产成品成本分配">#REF!</definedName>
-    <definedName name="产成品入库单22">#REF!</definedName>
-    <definedName name="成品入库">#REF!</definedName>
-    <definedName name="出库">#REF!</definedName>
-    <definedName name="柜型">#REF!</definedName>
-    <definedName name="_xlnm.Recorder" hidden="1">#REF!</definedName>
-    <definedName name="品">#REF!</definedName>
-    <definedName name="日期及时间">#REF!</definedName>
     <definedName name="入">#REF!</definedName>
     <definedName name="入库单">#REF!</definedName>
+    <definedName name="出库">#REF!</definedName>
     <definedName name="原料出库">#REF!</definedName>
+    <definedName name="品">#REF!</definedName>
+    <definedName name="成品入库">#REF!</definedName>
+    <definedName name="日期及时间">#REF!</definedName>
+    <definedName name="柜型">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3545,11 +3545,9 @@
   </si>
   <si>
     <t>SOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Kuma e-Box 2.0 (Starter Kit)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3557,20 +3555,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;£&quot;* #,##0.000_-;\-&quot;£&quot;* #,##0.000_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;£&quot;* #,##0.000_-;\-&quot;£&quot;* #,##0.000_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3578,7 +3576,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3586,21 +3584,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3631,7 +3629,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3644,7 +3642,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3655,8 +3653,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币" xfId="1" builtinId="4"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3672,9 +3670,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3712,7 +3710,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3818,7 +3816,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3960,7 +3958,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3969,17 +3967,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DA7849-36A6-445E-B4F4-F3A436346D30}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
     <col min="2" max="2" width="36.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="22" style="5" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.4140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.75" style="1"/>
+    <col min="5" max="5" width="17.33203125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -3996,7 +3994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -4013,7 +4011,7 @@
         <v>0.58390181771409322</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -4030,7 +4028,7 @@
         <v>0.88487248063111124</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -4047,7 +4045,7 @@
         <v>4.4655219929599719</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -4064,7 +4062,7 @@
         <v>8.9415813015774095</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
@@ -4081,7 +4079,7 @@
         <v>2.9291453731167607</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
@@ -4098,7 +4096,7 @@
         <v>2.9854310744157666</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
@@ -4115,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
@@ -4132,7 +4130,7 @@
         <v>4.5603940138979091</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
@@ -4149,11 +4147,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="6">
@@ -4166,7 +4164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -4183,7 +4181,7 @@
         <v>0.95806469850202569</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
@@ -4200,7 +4198,7 @@
         <v>1.4298321335598072</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
@@ -4217,7 +4215,7 @@
         <v>2.1608990343878305</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
@@ -4234,7 +4232,7 @@
         <v>2.2029299095160635</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
@@ -4251,7 +4249,7 @@
         <v>2.4868060233725853</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
@@ -4268,7 +4266,7 @@
         <v>0.92983179350962808</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>11</v>
       </c>
@@ -4286,7 +4284,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{A6DA7849-36A6-445E-B4F4-F3A436346D30}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
